--- a/Master Data.xlsx
+++ b/Master Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProPackHub\apps\estimation-studio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{407C2A2E-20D3-4B0A-A003-60AE334281A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CDA74A5-795D-4A6D-A27D-AFC79AE2CABB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Substrate" sheetId="1" r:id="rId1"/>
@@ -20,12 +20,14 @@
     <sheet name="Unit" sheetId="5" r:id="rId5"/>
     <sheet name="PT" sheetId="6" r:id="rId6"/>
     <sheet name="RM Type" sheetId="7" r:id="rId7"/>
+    <sheet name="Printing Web" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="Adhesive">tblAdhesive[Grade]</definedName>
     <definedName name="BOPP_Transparent">tblSubstrates[Substrate Grade]</definedName>
     <definedName name="InkCoating">tblInkCoating[Grade]</definedName>
     <definedName name="Packaging">tblPackaging[Grade]</definedName>
+    <definedName name="PrintingWeb">tblPrintingWeb[Printing Web]</definedName>
     <definedName name="Ptypes">tblPtypes[Product Type]</definedName>
     <definedName name="SubstrateFamily">tblSubstrates[Substrate Family]</definedName>
     <definedName name="Type">tblRMTypes[RM Type]</definedName>
@@ -49,7 +51,31 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="135">
+  <si>
+    <t>Product Type</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Roll</t>
+  </si>
+  <si>
+    <t>roll</t>
+  </si>
+  <si>
+    <t>Sleeve</t>
+  </si>
+  <si>
+    <t>sleeve</t>
+  </si>
+  <si>
+    <t>Bag</t>
+  </si>
+  <si>
+    <t>pouch</t>
+  </si>
   <si>
     <t>Substrate Family</t>
   </si>
@@ -393,31 +419,43 @@
     <t>Roll 500 LM</t>
   </si>
   <si>
-    <t>Product Type</t>
-  </si>
-  <si>
-    <t>Roll</t>
-  </si>
-  <si>
-    <t>Sleeve</t>
-  </si>
-  <si>
     <t>RM Type</t>
   </si>
   <si>
     <t>Substrate</t>
   </si>
   <si>
-    <t>Ink</t>
-  </si>
-  <si>
     <t>Adhesive</t>
   </si>
   <si>
     <t>Packaging</t>
   </si>
   <si>
-    <t>Bag</t>
+    <t>Printing Web</t>
+  </si>
+  <si>
+    <t>Ink System</t>
+  </si>
+  <si>
+    <t>Wide Web</t>
+  </si>
+  <si>
+    <t>wide_web</t>
+  </si>
+  <si>
+    <t>Ink SB</t>
+  </si>
+  <si>
+    <t>Narrow Web</t>
+  </si>
+  <si>
+    <t>narrow_web</t>
+  </si>
+  <si>
+    <t>Ink UV</t>
+  </si>
+  <si>
+    <t>Ink &amp; Coating</t>
   </si>
 </sst>
 </file>
@@ -544,10 +582,11 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="tblPtypes" displayName="tblPtypes" ref="A1:A4">
-  <autoFilter ref="A1:A4" xr:uid="{00000000-0009-0000-0100-000006000000}"/>
-  <tableColumns count="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="tblPtypes" displayName="tblPtypes" ref="A1:B4">
+  <autoFilter ref="A1:B4" xr:uid="{00000000-0009-0000-0100-000006000000}"/>
+  <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="Product Type"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Code"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -558,6 +597,19 @@
   <autoFilter ref="A1:A5" xr:uid="{00000000-0009-0000-0100-000007000000}"/>
   <tableColumns count="1">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="RM Type"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{00000000-000C-0000-FFFF-FFFF07000000}" name="tblPrintingWeb" displayName="tblPrintingWeb" ref="A1:D3">
+  <autoFilter ref="A1:D3" xr:uid="{00000000-0009-0000-0100-000008000000}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0700-000001000000}" name="Printing Web"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="Code"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0700-000003000000}" name="Ink System"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0700-000004000000}" name="Solid %"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -899,33 +951,33 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G1" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C2">
         <v>0.91</v>
@@ -943,10 +995,10 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C3">
         <v>0.91</v>
@@ -955,7 +1007,7 @@
         <v>100</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F3">
         <v>2.5</v>
@@ -963,10 +1015,10 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C4">
         <v>0.95</v>
@@ -975,7 +1027,7 @@
         <v>100</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F4">
         <v>2.6</v>
@@ -983,10 +1035,10 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C5">
         <v>0.7</v>
@@ -995,7 +1047,7 @@
         <v>100</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F5">
         <v>2.6</v>
@@ -1003,10 +1055,10 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C6">
         <v>0.91</v>
@@ -1015,7 +1067,7 @@
         <v>100</v>
       </c>
       <c r="E6" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F6">
         <v>2.6</v>
@@ -1023,10 +1075,10 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="C7">
         <v>0.91</v>
@@ -1035,7 +1087,7 @@
         <v>100</v>
       </c>
       <c r="E7" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F7">
         <v>4.7</v>
@@ -1043,10 +1095,10 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C8">
         <v>0.91</v>
@@ -1055,7 +1107,7 @@
         <v>100</v>
       </c>
       <c r="E8" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F8">
         <v>2.5</v>
@@ -1063,10 +1115,10 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="C9">
         <v>0.62</v>
@@ -1075,7 +1127,7 @@
         <v>100</v>
       </c>
       <c r="E9" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F9">
         <v>2.85</v>
@@ -1083,10 +1135,10 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="C10">
         <v>0.91</v>
@@ -1095,7 +1147,7 @@
         <v>100</v>
       </c>
       <c r="E10" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F10">
         <v>2.8</v>
@@ -1103,10 +1155,10 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="C11">
         <v>1.4</v>
@@ -1115,7 +1167,7 @@
         <v>100</v>
       </c>
       <c r="E11" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="F11">
         <v>2.15</v>
@@ -1123,10 +1175,10 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="C12">
         <v>1.4</v>
@@ -1135,7 +1187,7 @@
         <v>100</v>
       </c>
       <c r="E12" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F12">
         <v>2.25</v>
@@ -1143,10 +1195,10 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="C13">
         <v>1.4</v>
@@ -1155,7 +1207,7 @@
         <v>100</v>
       </c>
       <c r="E13" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="F13">
         <v>2.5</v>
@@ -1163,10 +1215,10 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="C14">
         <v>1.4</v>
@@ -1175,7 +1227,7 @@
         <v>100</v>
       </c>
       <c r="E14" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F14">
         <v>2.6</v>
@@ -1183,10 +1235,10 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C15">
         <v>1.4</v>
@@ -1195,7 +1247,7 @@
         <v>100</v>
       </c>
       <c r="E15" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F15">
         <v>2.7</v>
@@ -1203,10 +1255,10 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="C16">
         <v>1.4</v>
@@ -1215,7 +1267,7 @@
         <v>100</v>
       </c>
       <c r="E16" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F16">
         <v>2.9</v>
@@ -1223,10 +1275,10 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C17">
         <v>1.4</v>
@@ -1235,7 +1287,7 @@
         <v>100</v>
       </c>
       <c r="E17" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F17">
         <v>2.2999999999999998</v>
@@ -1243,10 +1295,10 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="B18" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C18">
         <v>1.4</v>
@@ -1255,7 +1307,7 @@
         <v>100</v>
       </c>
       <c r="E18" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="F18">
         <v>2.8</v>
@@ -1263,10 +1315,10 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="B19" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C19">
         <v>2.4</v>
@@ -1275,7 +1327,7 @@
         <v>100</v>
       </c>
       <c r="E19" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="F19">
         <v>2.8</v>
@@ -1283,10 +1335,10 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B20" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C20">
         <v>0.92</v>
@@ -1295,7 +1347,7 @@
         <v>100</v>
       </c>
       <c r="E20" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="F20">
         <v>1.7</v>
@@ -1303,10 +1355,10 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B21" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="C21">
         <v>0.93</v>
@@ -1315,7 +1367,7 @@
         <v>100</v>
       </c>
       <c r="E21" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="F21">
         <v>1.75</v>
@@ -1323,10 +1375,10 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B22" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="C22">
         <v>0.95</v>
@@ -1335,7 +1387,7 @@
         <v>100</v>
       </c>
       <c r="E22" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="F22">
         <v>2.75</v>
@@ -1343,10 +1395,10 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B23" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="C23">
         <v>0.92</v>
@@ -1355,7 +1407,7 @@
         <v>100</v>
       </c>
       <c r="E23" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="F23">
         <v>1.8</v>
@@ -1363,10 +1415,10 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B24" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="C24">
         <v>0.92</v>
@@ -1375,7 +1427,7 @@
         <v>100</v>
       </c>
       <c r="E24" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="F24">
         <v>2.2000000000000002</v>
@@ -1383,10 +1435,10 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="B25" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="C25">
         <v>0.9</v>
@@ -1395,7 +1447,7 @@
         <v>100</v>
       </c>
       <c r="E25" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="F25">
         <v>2.1</v>
@@ -1403,10 +1455,10 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="B26" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="C26">
         <v>0.9</v>
@@ -1415,7 +1467,7 @@
         <v>100</v>
       </c>
       <c r="E26" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="F26">
         <v>2.4</v>
@@ -1423,10 +1475,10 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="B27" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="C27">
         <v>0.92</v>
@@ -1435,7 +1487,7 @@
         <v>100</v>
       </c>
       <c r="E27" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="F27">
         <v>2.5</v>
@@ -1443,10 +1495,10 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="B28" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C28">
         <v>0.9</v>
@@ -1455,7 +1507,7 @@
         <v>100</v>
       </c>
       <c r="E28" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="F28">
         <v>2.5</v>
@@ -1463,10 +1515,10 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="B29" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="C29">
         <v>0.9</v>
@@ -1475,7 +1527,7 @@
         <v>100</v>
       </c>
       <c r="E29" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="F29">
         <v>2.2999999999999998</v>
@@ -1483,10 +1535,10 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="B30" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="C30">
         <v>1.1499999999999999</v>
@@ -1495,7 +1547,7 @@
         <v>100</v>
       </c>
       <c r="E30" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="F30">
         <v>2.5</v>
@@ -1503,10 +1555,10 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="B31" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="C31">
         <v>1.1499999999999999</v>
@@ -1515,7 +1567,7 @@
         <v>100</v>
       </c>
       <c r="E31" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="F31">
         <v>6</v>
@@ -1523,10 +1575,10 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="B32" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="C32">
         <v>1.06</v>
@@ -1535,7 +1587,7 @@
         <v>100</v>
       </c>
       <c r="E32" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="F32">
         <v>2.5</v>
@@ -1543,10 +1595,10 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="B33" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C33">
         <v>2.7</v>
@@ -1555,7 +1607,7 @@
         <v>100</v>
       </c>
       <c r="E33" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="F33">
         <v>4.5</v>
@@ -1563,10 +1615,10 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="B34" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="C34">
         <v>0.95</v>
@@ -1584,10 +1636,10 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="B35" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="C35">
         <v>0.78</v>
@@ -1605,10 +1657,10 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="B36" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="C36">
         <v>0.82</v>
@@ -1626,10 +1678,10 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="B37" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="C37">
         <v>0.95</v>
@@ -1647,10 +1699,10 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="B38" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C38">
         <v>1.05</v>
@@ -1668,10 +1720,10 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="B39" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="C39">
         <v>0.95</v>
@@ -1689,10 +1741,10 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="B40" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="C40">
         <v>1</v>
@@ -1710,10 +1762,10 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="B41" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="C41">
         <v>1.35</v>
@@ -1722,7 +1774,7 @@
         <v>100</v>
       </c>
       <c r="E41" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F41">
         <v>1.5</v>
@@ -1730,10 +1782,10 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="B42" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="C42">
         <v>1.35</v>
@@ -1742,7 +1794,7 @@
         <v>100</v>
       </c>
       <c r="E42" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="F42">
         <v>2.5</v>
@@ -1750,10 +1802,10 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="B43" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="C43">
         <v>1.32</v>
@@ -1762,7 +1814,7 @@
         <v>100</v>
       </c>
       <c r="E43" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="F43">
         <v>1.9</v>
@@ -1770,10 +1822,10 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="B44" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="C44">
         <v>1.32</v>
@@ -1782,7 +1834,7 @@
         <v>100</v>
       </c>
       <c r="E44" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="F44">
         <v>5</v>
@@ -1790,10 +1842,10 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="B45" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="C45">
         <v>1.24</v>
@@ -1802,7 +1854,7 @@
         <v>100</v>
       </c>
       <c r="E45" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="F45">
         <v>5</v>
@@ -1810,10 +1862,10 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="B46" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="C46">
         <v>1.21</v>
@@ -1822,7 +1874,7 @@
         <v>100</v>
       </c>
       <c r="E46" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="F46">
         <v>4.8</v>
@@ -1830,10 +1882,10 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="B47" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="C47">
         <v>1.1299999999999999</v>
@@ -1842,7 +1894,7 @@
         <v>100</v>
       </c>
       <c r="E47" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="F47">
         <v>4.5</v>
@@ -1850,10 +1902,10 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="B48" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="C48">
         <v>2.13</v>
@@ -1862,7 +1914,7 @@
         <v>100</v>
       </c>
       <c r="E48" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="F48">
         <v>5.5</v>
@@ -1891,30 +1943,30 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="B1" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="C1" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="B2" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -1929,10 +1981,10 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="B3" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -1947,10 +1999,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="B4" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -1965,10 +2017,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="B5" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -1983,10 +2035,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="B6" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -2001,10 +2053,10 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="B7" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -2019,10 +2071,10 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="B8" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -2037,10 +2089,10 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="B9" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -2055,10 +2107,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="B10" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -2073,10 +2125,10 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="B11" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -2091,10 +2143,10 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="B12" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -2109,10 +2161,10 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="B13" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -2127,10 +2179,10 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="B14" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -2158,30 +2210,30 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="B1" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="C1" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="B2" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -2196,10 +2248,10 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="B3" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -2214,10 +2266,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="B4" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -2245,36 +2297,36 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="B1" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="C1" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="B2" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="C2" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="D2" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="E2" t="str">
         <f>B2</f>
@@ -2283,16 +2335,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="B3" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="C3" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="D3" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="E3" t="str">
         <f>B3</f>
@@ -2301,16 +2353,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="B4" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="C4" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="D4" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="E4" t="str">
         <f>B4</f>
@@ -2332,32 +2384,32 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -2370,30 +2422,42 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>122</v>
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -2408,30 +2472,92 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>119</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>121</v>
+        <v>125</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C3" t="s">
+        <v>133</v>
+      </c>
+      <c r="D3">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
